--- a/Ammoniak/Ammoniak_Brownfield_Leuna/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_Leuna/Datenbank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_Memmingen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1A1055-5B14-4C4D-9AD9-57BAFC752D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C31FB3-2574-427B-9214-11780185F055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="297">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -991,12 +991,6 @@
   </si>
   <si>
     <t>calc_cost_nh3</t>
-  </si>
-  <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
     <t>Verkaufspreiseanalyse</t>
@@ -1159,7 +1153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1220,7 +1214,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1264,16 +1257,16 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1284,29 +1277,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1627,10 +1620,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="64" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1647,8 +1640,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="56"/>
-      <c r="B3" s="66"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="65"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1663,8 +1656,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="56"/>
-      <c r="B4" s="66"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="65"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1672,15 +1665,15 @@
         <v>28</v>
       </c>
       <c r="E4" s="21">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="56"/>
-      <c r="B5" s="66"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="65"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1695,8 +1688,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="66"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="65"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1711,8 +1704,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="56"/>
-      <c r="B7" s="66"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="65"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1727,8 +1720,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
-      <c r="B8" s="67" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="66" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1745,8 +1738,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="56"/>
-      <c r="B9" s="66"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="65"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1761,8 +1754,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="66"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="65"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -1777,8 +1770,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="56"/>
-      <c r="B11" s="66"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="65"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -1793,8 +1786,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
-      <c r="B12" s="66"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="65"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1809,8 +1802,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="56"/>
-      <c r="B13" s="66"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="65"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1825,8 +1818,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="56"/>
-      <c r="B14" s="66"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="65"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -1841,8 +1834,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="68"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -1857,8 +1850,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="56"/>
-      <c r="B16" s="59" t="s">
+      <c r="A16" s="55"/>
+      <c r="B16" s="58" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -1876,8 +1869,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="56"/>
-      <c r="B17" s="59"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="58"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -1892,8 +1885,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="59"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="58"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -1908,8 +1901,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
-      <c r="B19" s="59"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="58"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -1924,8 +1917,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="56"/>
-      <c r="B20" s="59"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="58"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -1940,10 +1933,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -1960,8 +1953,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="56"/>
-      <c r="B22" s="59"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="58"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -1976,8 +1969,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="56"/>
-      <c r="B23" s="59"/>
+      <c r="A23" s="55"/>
+      <c r="B23" s="58"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -1992,8 +1985,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="56"/>
-      <c r="B24" s="59"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="58"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2008,8 +2001,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
-      <c r="B25" s="59"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="58"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2024,8 +2017,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="56"/>
-      <c r="B26" s="59"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="58"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2040,8 +2033,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
-      <c r="B27" s="59"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="58"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2056,8 +2049,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="56"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="55"/>
+      <c r="B28" s="58"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2072,8 +2065,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
-      <c r="B29" s="60" t="s">
+      <c r="A29" s="55"/>
+      <c r="B29" s="59" t="s">
         <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2090,8 +2083,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="56"/>
-      <c r="B30" s="63"/>
+      <c r="A30" s="55"/>
+      <c r="B30" s="62"/>
       <c r="C30" s="49" t="s">
         <v>23</v>
       </c>
@@ -2107,8 +2100,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
-      <c r="B31" s="63"/>
+      <c r="A31" s="55"/>
+      <c r="B31" s="62"/>
       <c r="C31" s="49" t="s">
         <v>18</v>
       </c>
@@ -2123,8 +2116,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
-      <c r="B32" s="63"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="49" t="s">
         <v>19</v>
       </c>
@@ -2139,8 +2132,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="56"/>
-      <c r="B33" s="63"/>
+      <c r="A33" s="55"/>
+      <c r="B33" s="62"/>
       <c r="C33" s="49" t="s">
         <v>47</v>
       </c>
@@ -2155,8 +2148,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56"/>
-      <c r="B34" s="63"/>
+      <c r="A34" s="55"/>
+      <c r="B34" s="62"/>
       <c r="C34" s="49" t="s">
         <v>48</v>
       </c>
@@ -2171,8 +2164,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="63"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="62"/>
       <c r="C35" s="49" t="s">
         <v>115</v>
       </c>
@@ -2187,8 +2180,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="56"/>
-      <c r="B36" s="63"/>
+      <c r="A36" s="55"/>
+      <c r="B36" s="62"/>
       <c r="C36" s="49" t="s">
         <v>114</v>
       </c>
@@ -2203,8 +2196,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="56"/>
-      <c r="B37" s="63"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="62"/>
       <c r="C37" s="49" t="s">
         <v>15</v>
       </c>
@@ -2219,8 +2212,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="57"/>
-      <c r="B38" s="64"/>
+      <c r="A38" s="56"/>
+      <c r="B38" s="63"/>
       <c r="C38" s="15" t="s">
         <v>17</v>
       </c>
@@ -2235,7 +2228,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="54" t="s">
         <v>86</v>
       </c>
       <c r="B39" s="11" t="s">
@@ -2255,8 +2248,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="60" t="s">
+      <c r="A40" s="55"/>
+      <c r="B40" s="59" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -2273,8 +2266,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="59"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="58"/>
       <c r="C41" t="s">
         <v>12</v>
       </c>
@@ -2289,8 +2282,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="59"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="58"/>
       <c r="C42" t="s">
         <v>19</v>
       </c>
@@ -2305,8 +2298,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="59"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="58"/>
       <c r="C43" t="s">
         <v>20</v>
       </c>
@@ -2321,8 +2314,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="56"/>
-      <c r="B44" s="59"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="58"/>
       <c r="C44" t="s">
         <v>15</v>
       </c>
@@ -2337,8 +2330,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="59"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="58"/>
       <c r="C45" t="s">
         <v>82</v>
       </c>
@@ -2353,8 +2346,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="56"/>
-      <c r="B46" s="61"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="60"/>
       <c r="C46" s="5" t="s">
         <v>17</v>
       </c>
@@ -2369,8 +2362,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="56"/>
-      <c r="B47" s="60" t="s">
+      <c r="A47" s="55"/>
+      <c r="B47" s="59" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -2387,8 +2380,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="56"/>
-      <c r="B48" s="59"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="58"/>
       <c r="C48" t="s">
         <v>12</v>
       </c>
@@ -2403,8 +2396,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="56"/>
-      <c r="B49" s="59"/>
+      <c r="A49" s="55"/>
+      <c r="B49" s="58"/>
       <c r="C49" t="s">
         <v>19</v>
       </c>
@@ -2419,8 +2412,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="56"/>
-      <c r="B50" s="59"/>
+      <c r="A50" s="55"/>
+      <c r="B50" s="58"/>
       <c r="C50" t="s">
         <v>20</v>
       </c>
@@ -2435,8 +2428,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="56"/>
-      <c r="B51" s="59"/>
+      <c r="A51" s="55"/>
+      <c r="B51" s="58"/>
       <c r="C51" t="s">
         <v>15</v>
       </c>
@@ -2451,8 +2444,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="56"/>
-      <c r="B52" s="59"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="58"/>
       <c r="C52" t="s">
         <v>82</v>
       </c>
@@ -2467,8 +2460,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="57"/>
-      <c r="B53" s="62"/>
+      <c r="A53" s="56"/>
+      <c r="B53" s="61"/>
       <c r="C53" s="15" t="s">
         <v>17</v>
       </c>
@@ -2483,7 +2476,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="55" t="s">
+      <c r="A54" s="54" t="s">
         <v>90</v>
       </c>
       <c r="B54" s="17" t="s">
@@ -2496,14 +2489,14 @@
         <v>92</v>
       </c>
       <c r="E54" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="56"/>
+      <c r="A55" s="55"/>
       <c r="B55" s="18" t="s">
         <v>93</v>
       </c>
@@ -2521,7 +2514,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="57"/>
+      <c r="A56" s="56"/>
       <c r="B56" s="1" t="s">
         <v>94</v>
       </c>
@@ -2560,7 +2553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -2593,10 +2586,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="75" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="28" t="s">
@@ -2611,8 +2604,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="75"/>
-      <c r="B3" s="79"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="13" t="s">
         <v>135</v>
       </c>
@@ -2625,8 +2618,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
-      <c r="B4" s="79"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="69"/>
       <c r="C4" s="13" t="s">
         <v>102</v>
       </c>
@@ -2639,8 +2632,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
-      <c r="B5" s="79"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="13" t="s">
         <v>171</v>
       </c>
@@ -2653,8 +2646,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="75"/>
-      <c r="B6" s="79"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="69"/>
       <c r="C6" s="13" t="s">
         <v>183</v>
       </c>
@@ -2667,8 +2660,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
-      <c r="B7" s="79"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="69"/>
       <c r="C7" s="13" t="s">
         <v>201</v>
       </c>
@@ -2681,8 +2674,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75"/>
-      <c r="B8" s="79"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="69"/>
       <c r="C8" s="13" t="s">
         <v>249</v>
       </c>
@@ -2695,8 +2688,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="75"/>
-      <c r="B9" s="79"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="69"/>
       <c r="C9" s="13" t="s">
         <v>215</v>
       </c>
@@ -2709,8 +2702,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="75"/>
-      <c r="B10" s="79"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="69"/>
       <c r="C10" s="13" t="s">
         <v>239</v>
       </c>
@@ -2723,13 +2716,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="75"/>
-      <c r="B11" s="79"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="69"/>
       <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="75"/>
-      <c r="B12" s="81" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
@@ -2744,8 +2737,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="75"/>
-      <c r="B13" s="79"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="13" t="s">
         <v>176</v>
       </c>
@@ -2758,8 +2751,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="75"/>
-      <c r="B14" s="79"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="13" t="s">
         <v>179</v>
       </c>
@@ -2772,8 +2765,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="79"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="13" t="s">
         <v>180</v>
       </c>
@@ -2786,8 +2779,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
-      <c r="B16" s="79"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="13" t="s">
         <v>102</v>
       </c>
@@ -2800,8 +2793,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
-      <c r="B17" s="79"/>
+      <c r="A17" s="74"/>
+      <c r="B17" s="69"/>
       <c r="C17" s="13" t="s">
         <v>183</v>
       </c>
@@ -2814,8 +2807,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
-      <c r="B18" s="79"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="13" t="s">
         <v>201</v>
       </c>
@@ -2828,8 +2821,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
-      <c r="B19" s="79"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="13" t="s">
         <v>249</v>
       </c>
@@ -2842,8 +2835,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="75"/>
-      <c r="B20" s="79"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="13" t="s">
         <v>215</v>
       </c>
@@ -2856,8 +2849,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
-      <c r="B21" s="79"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="69"/>
       <c r="C21" s="13" t="s">
         <v>239</v>
       </c>
@@ -2870,16 +2863,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
-      <c r="B22" s="80"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="71"/>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
       <c r="E22" s="40"/>
       <c r="F22" s="39"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
-      <c r="B23" s="70" t="s">
+      <c r="A23" s="74"/>
+      <c r="B23" s="76" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="13" t="s">
@@ -2894,8 +2887,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75"/>
-      <c r="B24" s="70"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="76"/>
       <c r="C24" s="13" t="s">
         <v>135</v>
       </c>
@@ -2908,8 +2901,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="70"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="13" t="s">
         <v>102</v>
       </c>
@@ -2922,8 +2915,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="70"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="76"/>
       <c r="C26" s="13" t="s">
         <v>173</v>
       </c>
@@ -2936,8 +2929,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="70"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="13" t="s">
         <v>183</v>
       </c>
@@ -2950,8 +2943,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="70"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="13" t="s">
         <v>201</v>
       </c>
@@ -2964,8 +2957,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="75"/>
-      <c r="B29" s="70"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="76"/>
       <c r="C29" s="13" t="s">
         <v>249</v>
       </c>
@@ -2978,8 +2971,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="70"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="76"/>
       <c r="C30" s="13" t="s">
         <v>215</v>
       </c>
@@ -2992,8 +2985,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="70"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="76"/>
       <c r="C31" s="13" t="s">
         <v>239</v>
       </c>
@@ -3006,15 +2999,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="75"/>
-      <c r="B32" s="70"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="76"/>
       <c r="E32" s="35"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="82" t="s">
+      <c r="B33" s="78" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="28" t="s">
@@ -3025,12 +3018,12 @@
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="28" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
-      <c r="B34" s="70"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="13" t="s">
         <v>139</v>
       </c>
@@ -3039,12 +3032,12 @@
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="13" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
-      <c r="B35" s="70"/>
+      <c r="A35" s="74"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="13" t="s">
         <v>168</v>
       </c>
@@ -3057,8 +3050,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
-      <c r="B36" s="70"/>
+      <c r="A36" s="74"/>
+      <c r="B36" s="76"/>
       <c r="C36" s="13" t="s">
         <v>169</v>
       </c>
@@ -3071,8 +3064,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
-      <c r="B37" s="70"/>
+      <c r="A37" s="74"/>
+      <c r="B37" s="76"/>
       <c r="C37" s="13" t="s">
         <v>183</v>
       </c>
@@ -3085,8 +3078,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
-      <c r="B38" s="70"/>
+      <c r="A38" s="74"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="13" t="s">
         <v>201</v>
       </c>
@@ -3099,8 +3092,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
-      <c r="B39" s="70"/>
+      <c r="A39" s="74"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="13" t="s">
         <v>249</v>
       </c>
@@ -3113,8 +3106,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
-      <c r="B40" s="70"/>
+      <c r="A40" s="74"/>
+      <c r="B40" s="76"/>
       <c r="C40" s="13" t="s">
         <v>215</v>
       </c>
@@ -3127,8 +3120,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
-      <c r="B41" s="70"/>
+      <c r="A41" s="74"/>
+      <c r="B41" s="76"/>
       <c r="C41" s="13" t="s">
         <v>239</v>
       </c>
@@ -3141,13 +3134,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
-      <c r="B42" s="70"/>
+      <c r="A42" s="74"/>
+      <c r="B42" s="76"/>
       <c r="E42" s="35"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="75"/>
-      <c r="B43" s="69" t="s">
+      <c r="A43" s="74"/>
+      <c r="B43" s="79" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="37" t="s">
@@ -3162,8 +3155,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="75"/>
-      <c r="B44" s="70"/>
+      <c r="A44" s="74"/>
+      <c r="B44" s="76"/>
       <c r="C44" s="13" t="s">
         <v>141</v>
       </c>
@@ -3176,8 +3169,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="75"/>
-      <c r="B45" s="79"/>
+      <c r="A45" s="74"/>
+      <c r="B45" s="69"/>
       <c r="C45" s="13" t="s">
         <v>139</v>
       </c>
@@ -3190,8 +3183,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="75"/>
-      <c r="B46" s="79"/>
+      <c r="A46" s="74"/>
+      <c r="B46" s="69"/>
       <c r="C46" s="13" t="s">
         <v>135</v>
       </c>
@@ -3204,8 +3197,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
-      <c r="B47" s="79"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="69"/>
       <c r="C47" s="13" t="s">
         <v>156</v>
       </c>
@@ -3218,8 +3211,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="75"/>
-      <c r="B48" s="79"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="69"/>
       <c r="C48" s="13" t="s">
         <v>157</v>
       </c>
@@ -3232,8 +3225,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="75"/>
-      <c r="B49" s="79"/>
+      <c r="A49" s="74"/>
+      <c r="B49" s="69"/>
       <c r="C49" s="13" t="s">
         <v>183</v>
       </c>
@@ -3246,8 +3239,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
-      <c r="B50" s="79"/>
+      <c r="A50" s="74"/>
+      <c r="B50" s="69"/>
       <c r="C50" s="13" t="s">
         <v>201</v>
       </c>
@@ -3260,8 +3253,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
-      <c r="B51" s="79"/>
+      <c r="A51" s="74"/>
+      <c r="B51" s="69"/>
       <c r="C51" s="13" t="s">
         <v>249</v>
       </c>
@@ -3274,8 +3267,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
-      <c r="B52" s="79"/>
+      <c r="A52" s="74"/>
+      <c r="B52" s="69"/>
       <c r="C52" s="13" t="s">
         <v>215</v>
       </c>
@@ -3288,8 +3281,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
-      <c r="B53" s="79"/>
+      <c r="A53" s="74"/>
+      <c r="B53" s="69"/>
       <c r="C53" s="13" t="s">
         <v>239</v>
       </c>
@@ -3302,18 +3295,18 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
-      <c r="B54" s="83"/>
+      <c r="A54" s="77"/>
+      <c r="B54" s="80"/>
       <c r="C54" s="43"/>
       <c r="D54" s="43"/>
       <c r="E54" s="44"/>
       <c r="F54" s="43"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="73" t="s">
+      <c r="A55" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="77" t="s">
+      <c r="B55" s="75" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="28" t="s">
@@ -3328,8 +3321,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
-      <c r="B56" s="79"/>
+      <c r="A56" s="74"/>
+      <c r="B56" s="69"/>
       <c r="C56" s="13" t="s">
         <v>199</v>
       </c>
@@ -3342,13 +3335,13 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
-      <c r="B57" s="80"/>
+      <c r="A57" s="74"/>
+      <c r="B57" s="71"/>
       <c r="E57" s="33"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="69" t="s">
+      <c r="A58" s="74"/>
+      <c r="B58" s="79" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="37" t="s">
@@ -3363,8 +3356,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="70"/>
+      <c r="A59" s="74"/>
+      <c r="B59" s="76"/>
       <c r="C59" s="13" t="s">
         <v>135</v>
       </c>
@@ -3377,8 +3370,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="75"/>
-      <c r="B60" s="70"/>
+      <c r="A60" s="74"/>
+      <c r="B60" s="76"/>
       <c r="C60" s="13" t="s">
         <v>151</v>
       </c>
@@ -3391,8 +3384,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="75"/>
-      <c r="B61" s="70"/>
+      <c r="A61" s="74"/>
+      <c r="B61" s="76"/>
       <c r="C61" s="13" t="s">
         <v>183</v>
       </c>
@@ -3405,8 +3398,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="75"/>
-      <c r="B62" s="70"/>
+      <c r="A62" s="74"/>
+      <c r="B62" s="76"/>
       <c r="C62" s="13" t="s">
         <v>201</v>
       </c>
@@ -3419,8 +3412,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
-      <c r="B63" s="70"/>
+      <c r="A63" s="74"/>
+      <c r="B63" s="76"/>
       <c r="C63" s="13" t="s">
         <v>209</v>
       </c>
@@ -3433,8 +3426,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="75"/>
-      <c r="B64" s="70"/>
+      <c r="A64" s="74"/>
+      <c r="B64" s="76"/>
       <c r="C64" s="13" t="s">
         <v>249</v>
       </c>
@@ -3447,8 +3440,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="75"/>
-      <c r="B65" s="70"/>
+      <c r="A65" s="74"/>
+      <c r="B65" s="76"/>
       <c r="C65" s="13" t="s">
         <v>215</v>
       </c>
@@ -3461,8 +3454,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="75"/>
-      <c r="B66" s="70"/>
+      <c r="A66" s="74"/>
+      <c r="B66" s="76"/>
       <c r="C66" s="13" t="s">
         <v>239</v>
       </c>
@@ -3475,12 +3468,12 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="75"/>
-      <c r="B67" s="71"/>
+      <c r="A67" s="74"/>
+      <c r="B67" s="81"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="75"/>
-      <c r="B68" s="69" t="s">
+      <c r="A68" s="74"/>
+      <c r="B68" s="79" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="37" t="s">
@@ -3495,8 +3488,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="75"/>
-      <c r="B69" s="70"/>
+      <c r="A69" s="74"/>
+      <c r="B69" s="76"/>
       <c r="C69" s="13" t="s">
         <v>136</v>
       </c>
@@ -3509,8 +3502,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="75"/>
-      <c r="B70" s="70"/>
+      <c r="A70" s="74"/>
+      <c r="B70" s="76"/>
       <c r="C70" s="13" t="s">
         <v>149</v>
       </c>
@@ -3523,8 +3516,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="75"/>
-      <c r="B71" s="70"/>
+      <c r="A71" s="74"/>
+      <c r="B71" s="76"/>
       <c r="C71" s="13" t="s">
         <v>183</v>
       </c>
@@ -3537,8 +3530,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="75"/>
-      <c r="B72" s="70"/>
+      <c r="A72" s="74"/>
+      <c r="B72" s="76"/>
       <c r="C72" s="13" t="s">
         <v>201</v>
       </c>
@@ -3551,8 +3544,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="75"/>
-      <c r="B73" s="70"/>
+      <c r="A73" s="74"/>
+      <c r="B73" s="76"/>
       <c r="C73" s="13" t="s">
         <v>209</v>
       </c>
@@ -3565,8 +3558,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="75"/>
-      <c r="B74" s="70"/>
+      <c r="A74" s="74"/>
+      <c r="B74" s="76"/>
       <c r="C74" s="13" t="s">
         <v>249</v>
       </c>
@@ -3579,8 +3572,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="75"/>
-      <c r="B75" s="70"/>
+      <c r="A75" s="74"/>
+      <c r="B75" s="76"/>
       <c r="C75" s="13" t="s">
         <v>215</v>
       </c>
@@ -3593,8 +3586,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="75"/>
-      <c r="B76" s="70"/>
+      <c r="A76" s="74"/>
+      <c r="B76" s="76"/>
       <c r="C76" s="13" t="s">
         <v>239</v>
       </c>
@@ -3607,14 +3600,14 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="76"/>
-      <c r="B77" s="72"/>
+      <c r="A77" s="77"/>
+      <c r="B77" s="82"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="73" t="s">
+      <c r="A78" s="72" t="s">
         <v>90</v>
       </c>
-      <c r="B78" s="77" t="s">
+      <c r="B78" s="75" t="s">
         <v>87</v>
       </c>
       <c r="C78" s="28" t="s">
@@ -3630,312 +3623,312 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="74"/>
-      <c r="B79" s="78"/>
-      <c r="C79" s="53" t="s">
-        <v>291</v>
-      </c>
-      <c r="D79" s="53" t="s">
-        <v>290</v>
-      </c>
-      <c r="E79" s="54"/>
-      <c r="F79" s="53" t="s">
+      <c r="B79" s="69"/>
+      <c r="C79" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" s="35"/>
+      <c r="F79" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="75"/>
-      <c r="B80" s="79"/>
-      <c r="C80" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>191</v>
-      </c>
+      <c r="A80" s="74"/>
+      <c r="B80" s="71"/>
       <c r="E80" s="35"/>
-      <c r="F80" s="13" t="s">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="74"/>
+      <c r="B81" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="C81" s="37" t="s">
+        <v>161</v>
+      </c>
+      <c r="D81" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="E81" s="42"/>
+      <c r="F81" s="37" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="74"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E82" s="35"/>
+      <c r="F82" s="13" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="75"/>
-      <c r="B81" s="80"/>
-      <c r="E81" s="35"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="75"/>
-      <c r="B82" s="81" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="D82" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="E82" s="42"/>
-      <c r="F82" s="37" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="75"/>
-      <c r="B83" s="79"/>
-      <c r="C83" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="35"/>
-      <c r="F83" s="13" t="s">
-        <v>194</v>
-      </c>
+      <c r="A83" s="74"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="39"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="75"/>
-      <c r="B84" s="80"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="39"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="39"/>
+      <c r="A84" s="74"/>
+      <c r="B84" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E84" s="35"/>
+      <c r="F84" s="13" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="75"/>
-      <c r="B85" s="81" t="s">
-        <v>94</v>
-      </c>
+      <c r="A85" s="74"/>
+      <c r="B85" s="69"/>
       <c r="C85" s="13" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E85" s="35"/>
       <c r="F85" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="75"/>
-      <c r="B86" s="79"/>
-      <c r="C86" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" s="35"/>
-      <c r="F86" s="13" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="76"/>
-      <c r="B87" s="83"/>
-      <c r="C87" s="43"/>
-      <c r="D87" s="43"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="43"/>
+    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="77"/>
+      <c r="B86" s="80"/>
+      <c r="C86" s="43"/>
+      <c r="D86" s="43"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="43"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D87" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="73" t="s">
-        <v>211</v>
-      </c>
-      <c r="B88" s="77" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="D88" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="E88" s="28"/>
-      <c r="F88" s="28" t="s">
+      <c r="A88" s="73"/>
+      <c r="B88" s="69"/>
+      <c r="C88" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="F88" s="13" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="74"/>
-      <c r="B89" s="79"/>
-      <c r="C89" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>182</v>
-      </c>
+      <c r="A89" s="73"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="74"/>
-      <c r="B90" s="80"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39"/>
-      <c r="E90" s="39"/>
-      <c r="F90" s="39"/>
+      <c r="A90" s="73"/>
+      <c r="B90" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="74"/>
-      <c r="B91" s="81" t="s">
-        <v>234</v>
-      </c>
+      <c r="A91" s="73"/>
+      <c r="B91" s="69"/>
       <c r="C91" s="13" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F91" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="74"/>
-      <c r="B92" s="79"/>
+      <c r="A92" s="73"/>
+      <c r="B92" s="69"/>
       <c r="C92" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F92" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="74"/>
-      <c r="B93" s="79"/>
+      <c r="A93" s="73"/>
+      <c r="B93" s="69"/>
       <c r="C93" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F93" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="74"/>
-      <c r="B94" s="79"/>
+      <c r="A94" s="73"/>
+      <c r="B94" s="69"/>
       <c r="C94" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F94" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="74"/>
-      <c r="B95" s="79"/>
+      <c r="A95" s="73"/>
+      <c r="B95" s="69"/>
       <c r="C95" s="13" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="74"/>
-      <c r="B96" s="79"/>
-      <c r="C96" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>194</v>
+      <c r="A96" s="73"/>
+      <c r="B96" s="68" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="E96" s="37"/>
+      <c r="F96" s="37" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="74"/>
-      <c r="B97" s="81" t="s">
-        <v>263</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="D97" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37" t="s">
+      <c r="A97" s="73"/>
+      <c r="B97" s="70"/>
+      <c r="C97" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="D97" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="E97" s="53"/>
+      <c r="F97" s="53" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="74"/>
-      <c r="B98" s="78"/>
+      <c r="A98" s="73"/>
+      <c r="B98" s="70"/>
       <c r="C98" s="53" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D98" s="53" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E98" s="53"/>
       <c r="F98" s="53" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="74"/>
-      <c r="B99" s="78"/>
+      <c r="A99" s="73"/>
+      <c r="B99" s="70"/>
       <c r="C99" s="53" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D99" s="53" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E99" s="53"/>
       <c r="F99" s="53" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="74"/>
-      <c r="B100" s="78"/>
+      <c r="A100" s="73"/>
+      <c r="B100" s="70"/>
       <c r="C100" s="53" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D100" s="53" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E100" s="53"/>
       <c r="F100" s="53" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="74"/>
-      <c r="B101" s="78"/>
+      <c r="A101" s="73"/>
+      <c r="B101" s="70"/>
       <c r="C101" s="53" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D101" s="53" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E101" s="53"/>
       <c r="F101" s="53" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="74"/>
-      <c r="B102" s="78"/>
+      <c r="A102" s="73"/>
+      <c r="B102" s="70"/>
       <c r="C102" s="53" t="s">
-        <v>280</v>
-      </c>
-      <c r="D102" s="53" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>279</v>
       </c>
       <c r="E102" s="53"/>
       <c r="F102" s="53" t="s">
@@ -3943,71 +3936,71 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="74"/>
-      <c r="B103" s="78"/>
+      <c r="A103" s="73"/>
+      <c r="B103" s="70"/>
       <c r="C103" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>279</v>
+        <v>261</v>
+      </c>
+      <c r="D103" s="53" t="s">
+        <v>270</v>
       </c>
       <c r="E103" s="53"/>
-      <c r="F103" s="53" t="s">
+      <c r="F103" s="13" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="74"/>
-      <c r="B104" s="78"/>
+      <c r="A104" s="73"/>
+      <c r="B104" s="70"/>
       <c r="C104" s="53" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D104" s="53" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E104" s="53"/>
-      <c r="F104" s="13" t="s">
+      <c r="F104" s="53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="73"/>
+      <c r="B105" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="C105" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="E105" s="37"/>
+      <c r="F105" s="37" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="73"/>
+      <c r="B106" s="70"/>
+      <c r="C106" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="D106" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="E106" s="53"/>
+      <c r="F106" s="53" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="74"/>
-      <c r="B105" s="78"/>
-      <c r="C105" s="53" t="s">
-        <v>262</v>
-      </c>
-      <c r="D105" s="53" t="s">
-        <v>271</v>
-      </c>
-      <c r="E105" s="53"/>
-      <c r="F105" s="53" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="74"/>
-      <c r="B106" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="C106" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D106" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="E106" s="37"/>
-      <c r="F106" s="37" t="s">
-        <v>265</v>
-      </c>
-    </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="74"/>
-      <c r="B107" s="78"/>
+      <c r="A107" s="73"/>
+      <c r="B107" s="70"/>
       <c r="C107" s="53" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D107" s="53" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E107" s="53"/>
       <c r="F107" s="53" t="s">
@@ -4015,70 +4008,61 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="74"/>
-      <c r="B108" s="78"/>
-      <c r="C108" s="53" t="s">
-        <v>286</v>
-      </c>
-      <c r="D108" s="53" t="s">
-        <v>288</v>
-      </c>
-      <c r="E108" s="53"/>
-      <c r="F108" s="53" t="s">
-        <v>269</v>
+      <c r="A108" s="73"/>
+      <c r="B108" s="70"/>
+      <c r="C108" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="F108" s="13" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="74"/>
-      <c r="B109" s="78"/>
-      <c r="C109" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="F109" s="13" t="s">
-        <v>272</v>
-      </c>
+      <c r="A109" s="73"/>
+      <c r="B109" s="71"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="74"/>
-      <c r="B110" s="80"/>
+      <c r="A110" s="73"/>
+      <c r="B110" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="C110" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D110" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="E110" s="37"/>
+      <c r="F110" s="37" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="74"/>
-      <c r="B111" s="81" t="s">
-        <v>292</v>
-      </c>
-      <c r="C111" s="37" t="s">
+      <c r="A111" s="73"/>
+      <c r="B111" s="69"/>
+      <c r="C111" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="D111" s="37" t="s">
+      <c r="D111" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="E111" s="37"/>
-      <c r="F111" s="37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="74"/>
-      <c r="B112" s="79"/>
-      <c r="C112" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="F112" s="13" t="s">
+      <c r="F111" s="13" t="s">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="B106:B110"/>
-    <mergeCell ref="A88:A112"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="B68:B77"/>
+    <mergeCell ref="A78:A86"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B105:B109"/>
+    <mergeCell ref="A87:A111"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4086,17 +4070,12 @@
     <mergeCell ref="A33:A54"/>
     <mergeCell ref="B33:B42"/>
     <mergeCell ref="B43:B54"/>
-    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B84:B86"/>
     <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B105"/>
-    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B96:B104"/>
+    <mergeCell ref="B87:B89"/>
     <mergeCell ref="A55:A77"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="B68:B77"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
